--- a/data/trending_integrated_20261027_09.xlsx
+++ b/data/trending_integrated_20261027_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:Z4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1359000</v>
+        <v>1354500</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+6.59%</t>
+          <t>'+6.24%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.03</v>
       </c>
       <c r="E2" t="n">
-        <v>548</v>
+        <v>615</v>
       </c>
       <c r="F2" t="n">
-        <v>362</v>
+        <v>396</v>
       </c>
       <c r="G2" t="n">
-        <v>2202</v>
+        <v>2383</v>
       </c>
       <c r="H2" t="n">
         <v>48.66</v>
@@ -601,7 +601,7 @@
         <v>1346000</v>
       </c>
       <c r="L2" t="n">
-        <v>1360000</v>
+        <v>1364000</v>
       </c>
       <c r="M2" t="n">
         <v>1345000</v>
@@ -610,7 +610,7 @@
         <v>48.69</v>
       </c>
       <c r="O2" t="n">
-        <v>231836641000</v>
+        <v>478784102000</v>
       </c>
       <c r="P2" t="n">
         <v>2987000</v>
@@ -649,6 +649,190 @@
       <c r="Z2" t="inlineStr">
         <is>
           <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>222250</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>'+4.34%</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E3" t="n">
+        <v>571</v>
+      </c>
+      <c r="F3" t="n">
+        <v>360</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2543</v>
+      </c>
+      <c r="H3" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>213000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>222000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>223500</v>
+      </c>
+      <c r="M3" t="n">
+        <v>221500</v>
+      </c>
+      <c r="N3" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="O3" t="n">
+        <v>302242559500</v>
+      </c>
+      <c r="P3" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>글로벌 선물주가 호조 및 앤트로픽 상장 관련 기대감. 일부 정치적 내용 포함.</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>['선물주가', '앤트로픽', '주가']</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14940</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>'+1.70%</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E4" t="n">
+        <v>61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>48</v>
+      </c>
+      <c r="G4" t="n">
+        <v>165</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>14690</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14490</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15310</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14260</v>
+      </c>
+      <c r="N4" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17093129440</v>
+      </c>
+      <c r="P4" t="n">
+        <v>49800</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>8180</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>의료 AI 대장주로서의 입지 강화 전망. 신약 개발 활용 및 해외 수요 기대. 공매도 숏커버링 가능성 언급.</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>['의료 AI', '신약 개발', '공매도']</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>328130</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261027_09.xlsx
+++ b/data/trending_integrated_20261027_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z4"/>
+  <dimension ref="A1:Z7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,83 +563,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1354500</v>
+        <v>16770</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+6.24%</t>
+          <t>'+27.53%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>615</v>
+        <v>46</v>
       </c>
       <c r="F2" t="n">
-        <v>396</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>2383</v>
+        <v>110</v>
       </c>
       <c r="H2" t="n">
-        <v>48.66</v>
+        <v>4.13</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>1275000</v>
+        <v>13150</v>
       </c>
       <c r="K2" t="n">
-        <v>1346000</v>
+        <v>16280</v>
       </c>
       <c r="L2" t="n">
-        <v>1364000</v>
+        <v>17080</v>
       </c>
       <c r="M2" t="n">
-        <v>1345000</v>
+        <v>15720</v>
       </c>
       <c r="N2" t="n">
-        <v>48.69</v>
+        <v>4.28</v>
       </c>
       <c r="O2" t="n">
-        <v>478784102000</v>
+        <v>9807969995</v>
       </c>
       <c r="P2" t="n">
-        <v>2987000</v>
+        <v>28600</v>
       </c>
       <c r="Q2" t="n">
-        <v>501000</v>
+        <v>11050</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>미증시 반도체 급등 및 나스닥 하이닉스 ADR 폭등 관련 내용 언급. 단, 구체적인 근거 제시 부족.</t>
+          <t>나무가, 휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스 기반 급등. 텐버거 기대감 및 매물 부족 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['ADR', '야선물', '미증시']</t>
+          <t>['휴머노이드 로봇', '아틀라스', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -648,38 +648,38 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>222250</v>
+        <v>1366000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+4.34%</t>
+          <t>'+7.14%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>571</v>
+        <v>717</v>
       </c>
       <c r="F3" t="n">
-        <v>360</v>
+        <v>455</v>
       </c>
       <c r="G3" t="n">
-        <v>2543</v>
+        <v>2518</v>
       </c>
       <c r="H3" t="n">
-        <v>46.1</v>
+        <v>48.66</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,47 +687,47 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>213000</v>
+        <v>1275000</v>
       </c>
       <c r="K3" t="n">
-        <v>222000</v>
+        <v>1346000</v>
       </c>
       <c r="L3" t="n">
-        <v>223500</v>
+        <v>1375000</v>
       </c>
       <c r="M3" t="n">
-        <v>221500</v>
+        <v>1345000</v>
       </c>
       <c r="N3" t="n">
-        <v>46.11</v>
+        <v>48.69</v>
       </c>
       <c r="O3" t="n">
-        <v>302242559500</v>
+        <v>744182222000</v>
       </c>
       <c r="P3" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q3" t="n">
-        <v>94500</v>
+        <v>501000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>86000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>글로벌 선물주가 호조 및 앤트로픽 상장 관련 기대감. 일부 정치적 내용 포함.</t>
+          <t>미증시 반도체 급등 및 나스닥 하이닉스 ADR 폭등 관련 내용 언급. 단, 구체적인 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['선물주가', '앤트로픽', '주가']</t>
+          <t>['ADR', '야선물', '미증시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,97 +740,373 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14940</v>
+        <v>15040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.70%</t>
+          <t>'+5.77%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.46</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>165</v>
+        <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>7.82</v>
+        <v>10.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14690</v>
+        <v>14220</v>
       </c>
       <c r="K4" t="n">
-        <v>14490</v>
+        <v>14390</v>
       </c>
       <c r="L4" t="n">
-        <v>15310</v>
+        <v>15070</v>
       </c>
       <c r="M4" t="n">
-        <v>14260</v>
+        <v>14390</v>
       </c>
       <c r="N4" t="n">
-        <v>7.36</v>
+        <v>10.03</v>
       </c>
       <c r="O4" t="n">
-        <v>17093129440</v>
+        <v>10183143245</v>
       </c>
       <c r="P4" t="n">
-        <v>49800</v>
+        <v>40350</v>
       </c>
       <c r="Q4" t="n">
-        <v>8180</v>
+        <v>3320</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>84000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>의료 AI 대장주로서의 입지 강화 전망. 신약 개발 활용 및 해외 수요 기대. 공매도 숏커버링 가능성 언급.</t>
+          <t>대우건설, 실적 발표 후 영익 223% 폭증 확인. 공매도 관련 언급 및 주주 독려.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['의료 AI', '신약 개발', '공매도']</t>
+          <t>['영업이익 폭증', '실적 발표', '공매도']</t>
         </is>
       </c>
       <c r="X4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>047040</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>223250</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>'+4.81%</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E5" t="n">
+        <v>611</v>
+      </c>
+      <c r="F5" t="n">
+        <v>379</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2579</v>
+      </c>
+      <c r="H5" t="n">
+        <v>46.1</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>213000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>222000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>224500</v>
+      </c>
+      <c r="M5" t="n">
+        <v>221500</v>
+      </c>
+      <c r="N5" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>423272923000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>374500</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>94500</v>
+      </c>
+      <c r="R5" t="n">
+        <v>693000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>글로벌 선물주가 호조 및 앤트로픽 상장 관련 기대감. 일부 정치적 내용 포함.</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>['선물주가', '앤트로픽', '주가']</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>62300</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>'+4.18%</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" t="n">
+        <v>299</v>
+      </c>
+      <c r="H6" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>59800</v>
+      </c>
+      <c r="K6" t="n">
+        <v>60700</v>
+      </c>
+      <c r="L6" t="n">
+        <v>63900</v>
+      </c>
+      <c r="M6" t="n">
+        <v>60100</v>
+      </c>
+      <c r="N6" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="O6" t="n">
+        <v>82497500200</v>
+      </c>
+      <c r="P6" t="n">
+        <v>67300</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>23150</v>
+      </c>
+      <c r="R6" t="n">
+        <v>107000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>삼성E&amp;A, 최근 4일간 코스피 수익률 1위 달성. 외국인 역대급 매수세 유입 확인. 중동 관련 투자 기대감.</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>['삼성그룹주', '수익률 1위', '외국인 매수']</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14770</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>'+0.54%</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E7" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" t="n">
+        <v>54</v>
+      </c>
+      <c r="G7" t="n">
+        <v>189</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>14690</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14490</v>
+      </c>
+      <c r="L7" t="n">
+        <v>15340</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14260</v>
+      </c>
+      <c r="N7" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="O7" t="n">
+        <v>26285590560</v>
+      </c>
+      <c r="P7" t="n">
+        <v>49800</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>8180</v>
+      </c>
+      <c r="R7" t="n">
+        <v>43000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>루닛, 해외 수출 및 신약 개발 활용 기대감. 서밋테라퓨틱스와의 협력 언급. 외국인 대규모 매수세 유입.</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>['의료 AI', '해외 수출', '신약 개발']</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
         <v>2</v>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>328130</t>
         </is>

--- a/data/trending_integrated_20261027_09.xlsx
+++ b/data/trending_integrated_20261027_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16770</v>
+        <v>16490</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.53%</t>
+          <t>'+25.40%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H2" t="n">
         <v>4.13</v>
@@ -610,7 +610,7 @@
         <v>4.28</v>
       </c>
       <c r="O2" t="n">
-        <v>9807969995</v>
+        <v>10657278680</v>
       </c>
       <c r="P2" t="n">
         <v>28600</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>나무가, 휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스 기반 급등. 텐버거 기대감 및 매물 부족 언급.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스 기반, 텐버거 기대감 및 매물 공백 확인.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '아틀라스', '텐버거']</t>
+          <t>['휴머노이드', '아틀라스', '공급망']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1366000</v>
+        <v>1358000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+7.14%</t>
+          <t>'+6.51%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>-0.03</v>
       </c>
       <c r="E3" t="n">
-        <v>717</v>
+        <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>455</v>
+        <v>489</v>
       </c>
       <c r="G3" t="n">
-        <v>2518</v>
+        <v>2550</v>
       </c>
       <c r="H3" t="n">
         <v>48.66</v>
@@ -702,7 +702,7 @@
         <v>48.69</v>
       </c>
       <c r="O3" t="n">
-        <v>744182222000</v>
+        <v>909111670500</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미증시 반도체 급등 및 나스닥 하이닉스 ADR 폭등 관련 내용 언급. 단, 구체적인 근거 제시 부족.</t>
+          <t>미국 증시 반도체 섹터 강세 및 야간 선물 급등에 따른 SK하이닉스 주가 상승 기대감.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['ADR', '야선물', '미증시']</t>
+          <t>['반도체', '야간선물', '미증시']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15040</v>
+        <v>14970</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.77%</t>
+          <t>'+5.27%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="H4" t="n">
         <v>10.02</v>
@@ -785,7 +785,7 @@
         <v>14390</v>
       </c>
       <c r="L4" t="n">
-        <v>15070</v>
+        <v>15150</v>
       </c>
       <c r="M4" t="n">
         <v>14390</v>
@@ -794,7 +794,7 @@
         <v>10.03</v>
       </c>
       <c r="O4" t="n">
-        <v>10183143245</v>
+        <v>14236417635</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대우건설, 실적 발표 후 영익 223% 폭증 확인. 공매도 관련 언급 및 주주 독려.</t>
+          <t>영업이익 223% 폭증한 호실적 발표와 외국인, 기관의 지속적인 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['영업이익 폭증', '실적 발표', '공매도']</t>
+          <t>['실적', '영업이익', '매수세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>611</v>
+        <v>655</v>
       </c>
       <c r="F5" t="n">
-        <v>379</v>
+        <v>402</v>
       </c>
       <c r="G5" t="n">
-        <v>2579</v>
+        <v>2654</v>
       </c>
       <c r="H5" t="n">
         <v>46.1</v>
@@ -877,7 +877,7 @@
         <v>222000</v>
       </c>
       <c r="L5" t="n">
-        <v>224500</v>
+        <v>225000</v>
       </c>
       <c r="M5" t="n">
         <v>221500</v>
@@ -886,7 +886,7 @@
         <v>46.11</v>
       </c>
       <c r="O5" t="n">
-        <v>423272923000</v>
+        <v>578323432250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62300</v>
+        <v>62000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.18%</t>
+          <t>'+3.68%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G6" t="n">
-        <v>299</v>
+        <v>337</v>
       </c>
       <c r="H6" t="n">
         <v>40.44</v>
@@ -978,7 +978,7 @@
         <v>40.39</v>
       </c>
       <c r="O6" t="n">
-        <v>82497500200</v>
+        <v>96954151700</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A, 최근 4일간 코스피 수익률 1위 달성. 외국인 역대급 매수세 유입 확인. 중동 관련 투자 기대감.</t>
+          <t>삼성그룹주 중 저평가 분석에 따른 외국인 역대급 매수세 유입.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성그룹주', '수익률 1위', '외국인 매수']</t>
+          <t>['저평가', '외국인', '매수세']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14770</v>
+        <v>14390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.46</v>
       </c>
       <c r="E7" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G7" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H7" t="n">
         <v>7.82</v>
@@ -1070,7 +1070,7 @@
         <v>7.36</v>
       </c>
       <c r="O7" t="n">
-        <v>26285590560</v>
+        <v>29954687255</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>루닛, 해외 수출 및 신약 개발 활용 기대감. 서밋테라퓨틱스와의 협력 언급. 외국인 대규모 매수세 유입.</t>
+          <t>해외 수출 및 신약 개발 등 Lunit의 넓은 성장 전망과 프로그램/외국인 대규모 매수세.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 AI', '해외 수출', '신약 개발']</t>
+          <t>['수출', '신약개발', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20261027_09.xlsx
+++ b/data/trending_integrated_20261027_09.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16490</v>
+        <v>16740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.40%</t>
+          <t>'+27.30%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>-0.15</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G2" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H2" t="n">
         <v>4.13</v>
@@ -610,7 +610,7 @@
         <v>4.28</v>
       </c>
       <c r="O2" t="n">
-        <v>10657278680</v>
+        <v>12189341665</v>
       </c>
       <c r="P2" t="n">
         <v>28600</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 뉴스 기반, 텐버거 기대감 및 매물 공백 확인.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 소식과 업계 예상 상회하는 사업 성과에 대한 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드', '아틀라스', '공급망']</t>
+          <t>['휴머노이드 로봇', '공급망', '텐버거']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1358000</v>
+        <v>1357000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.51%</t>
+          <t>'+6.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -673,10 +673,10 @@
         <v>800</v>
       </c>
       <c r="F3" t="n">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="G3" t="n">
-        <v>2550</v>
+        <v>2357</v>
       </c>
       <c r="H3" t="n">
         <v>48.66</v>
@@ -702,7 +702,7 @@
         <v>48.69</v>
       </c>
       <c r="O3" t="n">
-        <v>909111670500</v>
+        <v>1015911077000</v>
       </c>
       <c r="P3" t="n">
         <v>2987000</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 증시 반도체 섹터 강세 및 야간 선물 급등에 따른 SK하이닉스 주가 상승 기대감.</t>
+          <t>미국 반도체 시장 강세 및 야간 선물 급등에 따른 주가 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '야간선물', '미증시']</t>
+          <t>['반도체', '야간 선물', '급등']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14970</v>
+        <v>14930</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+5.27%</t>
+          <t>'+4.99%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>152</v>
+        <v>179</v>
       </c>
       <c r="H4" t="n">
         <v>10.02</v>
@@ -794,7 +794,7 @@
         <v>10.03</v>
       </c>
       <c r="O4" t="n">
-        <v>14236417635</v>
+        <v>15569736740</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증한 호실적 발표와 외국인, 기관의 지속적인 매수세 확인.</t>
+          <t>영업이익 223% 폭증 등 호실적 발표와 외국인, 기관의 지속적인 매수세 확인.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', '영업이익', '매수세']</t>
+          <t>['실적', '영업이익', '기관 매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>655</v>
+        <v>680</v>
       </c>
       <c r="F5" t="n">
-        <v>402</v>
+        <v>419</v>
       </c>
       <c r="G5" t="n">
-        <v>2654</v>
+        <v>2723</v>
       </c>
       <c r="H5" t="n">
         <v>46.1</v>
@@ -886,7 +886,7 @@
         <v>46.11</v>
       </c>
       <c r="O5" t="n">
-        <v>578323432250</v>
+        <v>665329429250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>62000</v>
+        <v>61500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.68%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="H6" t="n">
         <v>40.44</v>
@@ -978,7 +978,7 @@
         <v>40.39</v>
       </c>
       <c r="O6" t="n">
-        <v>96954151700</v>
+        <v>107340551400</v>
       </c>
       <c r="P6" t="n">
         <v>67300</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성그룹주 중 저평가 분석에 따른 외국인 역대급 매수세 유입.</t>
+          <t>삼성그룹주 중 저평가 인식과 함께 외인 매수세 유입, 코스피 수익률 1위 달성.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '외국인', '매수세']</t>
+          <t>['저평가', '외인 매수', '수익률']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14390</v>
+        <v>14700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.46</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>190</v>
@@ -1070,7 +1070,7 @@
         <v>7.36</v>
       </c>
       <c r="O7" t="n">
-        <v>29954687255</v>
+        <v>32264738595</v>
       </c>
       <c r="P7" t="n">
         <v>49800</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 등 Lunit의 넓은 성장 전망과 프로그램/외국인 대규모 매수세.</t>
+          <t>해외 수출 및 신약 개발 활용 가능성에 기반한 의료 AI 분야의 성장 전망. 프로그램/외국인 대규모 매수 확인.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수출', '신약개발', '매수세']</t>
+          <t>['의료 AI', '해외 수출', '대규모 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">

--- a/data/trending_integrated_20261027_09.xlsx
+++ b/data/trending_integrated_20261027_09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z7"/>
+  <dimension ref="A1:Z9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>나무가</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16740</v>
+        <v>15830</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+27.30%</t>
+          <t>'+29.97%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-0.15</v>
+        <v>-0.41</v>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="H2" t="n">
-        <v>4.13</v>
+        <v>0.09</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>13150</v>
+        <v>12180</v>
       </c>
       <c r="K2" t="n">
-        <v>16280</v>
+        <v>12510</v>
       </c>
       <c r="L2" t="n">
-        <v>17080</v>
+        <v>15830</v>
       </c>
       <c r="M2" t="n">
-        <v>15720</v>
+        <v>12500</v>
       </c>
       <c r="N2" t="n">
-        <v>4.28</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>12189341665</v>
+        <v>39788169080</v>
       </c>
       <c r="P2" t="n">
-        <v>28600</v>
+        <v>28800</v>
       </c>
       <c r="Q2" t="n">
-        <v>11050</v>
+        <v>11550</v>
       </c>
       <c r="R2" t="n">
-        <v>-30000</v>
+        <v>31000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 소식과 업계 예상 상회하는 사업 성과에 대한 기대감.</t>
+          <t>멜콘, 삼성·SK 이어 美 'M사' 공급망 진입 뉴스 확인. HBM 및 데이터센터 관련 미래 성장성 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['휴머노이드 로봇', '공급망', '텐버거']</t>
+          <t>['공급망', 'HBM', '성장성']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,90 +648,90 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>190510</t>
+          <t>179880</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>나무가</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1357000</v>
+        <v>16640</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+6.43%</t>
+          <t>'+26.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.03</v>
+        <v>-0.15</v>
       </c>
       <c r="E3" t="n">
-        <v>800</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>477</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
-        <v>2357</v>
+        <v>115</v>
       </c>
       <c r="H3" t="n">
-        <v>48.66</v>
+        <v>4.13</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>1275000</v>
+        <v>13150</v>
       </c>
       <c r="K3" t="n">
-        <v>1346000</v>
+        <v>16280</v>
       </c>
       <c r="L3" t="n">
-        <v>1375000</v>
+        <v>17080</v>
       </c>
       <c r="M3" t="n">
-        <v>1345000</v>
+        <v>15720</v>
       </c>
       <c r="N3" t="n">
-        <v>48.69</v>
+        <v>4.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1015911077000</v>
+        <v>12793455420</v>
       </c>
       <c r="P3" t="n">
-        <v>2987000</v>
+        <v>28600</v>
       </c>
       <c r="Q3" t="n">
-        <v>501000</v>
+        <v>11050</v>
       </c>
       <c r="R3" t="n">
-        <v>86000</v>
+        <v>-30000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>미국 반도체 시장 강세 및 야간 선물 급등에 따른 주가 상승 기대감 형성.</t>
+          <t>휴머노이드 로봇 '아틀라스' 공급망 확정 및 텐버거 가능성 언급. 3D 센싱 관련 기술력 보유.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '야간 선물', '급등']</t>
+          <t>['로봇', '공급망', '3D센싱']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,38 +740,38 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>190510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14930</v>
+        <v>1359500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+4.99%</t>
+          <t>'+6.63%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E4" t="n">
-        <v>54</v>
+        <v>800</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>470</v>
       </c>
       <c r="G4" t="n">
-        <v>179</v>
+        <v>1890</v>
       </c>
       <c r="H4" t="n">
-        <v>10.02</v>
+        <v>48.66</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14220</v>
+        <v>1275000</v>
       </c>
       <c r="K4" t="n">
-        <v>14390</v>
+        <v>1346000</v>
       </c>
       <c r="L4" t="n">
-        <v>15150</v>
+        <v>1375000</v>
       </c>
       <c r="M4" t="n">
-        <v>14390</v>
+        <v>1345000</v>
       </c>
       <c r="N4" t="n">
-        <v>10.03</v>
+        <v>48.69</v>
       </c>
       <c r="O4" t="n">
-        <v>15569736740</v>
+        <v>1124052218500</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>501000</v>
       </c>
       <c r="R4" t="n">
-        <v>84000</v>
+        <v>86000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>영업이익 223% 폭증 등 호실적 발표와 외국인, 기관의 지속적인 매수세 확인.</t>
+          <t>다음 주 200 돌파 및 금일 대폭등 가능성 언급. 엔트로픽 공모자금 관련 내용 및 주주 환원 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['실적', '영업이익', '기관 매수']</t>
+          <t>['폭등', '주주환원', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>223250</v>
+        <v>223500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+4.81%</t>
+          <t>'+4.93%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>680</v>
+        <v>710</v>
       </c>
       <c r="F5" t="n">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="G5" t="n">
-        <v>2723</v>
+        <v>2760</v>
       </c>
       <c r="H5" t="n">
         <v>46.1</v>
@@ -886,7 +886,7 @@
         <v>46.11</v>
       </c>
       <c r="O5" t="n">
-        <v>665329429250</v>
+        <v>749891625250</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성E&amp;A</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>61500</v>
+        <v>14880</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+4.64%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>354</v>
+        <v>188</v>
       </c>
       <c r="H6" t="n">
-        <v>40.44</v>
+        <v>10.02</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>59800</v>
+        <v>14220</v>
       </c>
       <c r="K6" t="n">
-        <v>60700</v>
+        <v>14390</v>
       </c>
       <c r="L6" t="n">
-        <v>63900</v>
+        <v>15150</v>
       </c>
       <c r="M6" t="n">
-        <v>60100</v>
+        <v>14390</v>
       </c>
       <c r="N6" t="n">
-        <v>40.39</v>
+        <v>10.03</v>
       </c>
       <c r="O6" t="n">
-        <v>107340551400</v>
+        <v>21407896515</v>
       </c>
       <c r="P6" t="n">
-        <v>67300</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>23150</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>107000</v>
+        <v>84000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼성그룹주 중 저평가 인식과 함께 외인 매수세 유입, 코스피 수익률 1위 달성.</t>
+          <t>영업이익 223% 폭증 및 외국인, 기관의 꾸준한 매수세 확인. 실적 발표 호조에 대한 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['저평가', '외인 매수', '수익률']</t>
+          <t>['영업이익', '실적', '매수세']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,99 +1016,283 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028050</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>루닛</t>
+          <t>삼성E&amp;A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14700</v>
+        <v>62100</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+3.85%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.46</v>
+        <v>0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>190</v>
+        <v>405</v>
       </c>
       <c r="H7" t="n">
-        <v>7.82</v>
+        <v>40.44</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14690</v>
+        <v>59800</v>
       </c>
       <c r="K7" t="n">
-        <v>14490</v>
+        <v>60700</v>
       </c>
       <c r="L7" t="n">
-        <v>15340</v>
+        <v>63900</v>
       </c>
       <c r="M7" t="n">
-        <v>14260</v>
+        <v>60100</v>
       </c>
       <c r="N7" t="n">
-        <v>7.36</v>
+        <v>40.39</v>
       </c>
       <c r="O7" t="n">
-        <v>32264738595</v>
+        <v>116469328600</v>
       </c>
       <c r="P7" t="n">
-        <v>49800</v>
+        <v>67300</v>
       </c>
       <c r="Q7" t="n">
-        <v>8180</v>
+        <v>23150</v>
       </c>
       <c r="R7" t="n">
-        <v>43000</v>
+        <v>107000</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>해외 수출 및 신약 개발 활용 가능성에 기반한 의료 AI 분야의 성장 전망. 프로그램/외국인 대규모 매수 확인.</t>
+          <t>이재용 회장의 중동 방문 및 삼전닉스의 대규모 투자 뉴스를 기반으로 삼성그룹주 중 저평가되었으나, 내일 주가 하락 가능성에 대한 의견도 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.7</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['의료 AI', '해외 수출', '대규모 매수']</t>
+          <t>['저평가', '투자', '전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>028050</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>루닛</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>15110</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>'+2.86%</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E8" t="n">
+        <v>76</v>
+      </c>
+      <c r="F8" t="n">
+        <v>60</v>
+      </c>
+      <c r="G8" t="n">
+        <v>224</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>14690</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14490</v>
+      </c>
+      <c r="L8" t="n">
+        <v>15340</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14260</v>
+      </c>
+      <c r="N8" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="O8" t="n">
+        <v>36318946155</v>
+      </c>
+      <c r="P8" t="n">
+        <v>49800</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>8180</v>
+      </c>
+      <c r="R8" t="n">
+        <v>43000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>해외 수출 및 신약 개발 활용의 의미, Lunit의 넓은 성장 가능성 언급. 대규모 공매도 숏커버링 및 외국인, 연기금, 투신, 사모펀드의 대량 매수 확인.</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>['AI', '수출', '매수']</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
         <v>2</v>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>328130</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>16660</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>'+2.21%</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E9" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" t="n">
+        <v>31</v>
+      </c>
+      <c r="G9" t="n">
+        <v>96</v>
+      </c>
+      <c r="H9" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>16300</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16410</v>
+      </c>
+      <c r="L9" t="n">
+        <v>16730</v>
+      </c>
+      <c r="M9" t="n">
+        <v>16410</v>
+      </c>
+      <c r="N9" t="n">
+        <v>27.94</v>
+      </c>
+      <c r="O9" t="n">
+        <v>14423553650</v>
+      </c>
+      <c r="P9" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>16290</v>
+      </c>
+      <c r="R9" t="n">
+        <v>128000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>외국인 매수세가 꾸준히 언급되나, 주가는 고점 대비 큰 폭으로 하락한 상태. 조선주 전반의 하락세 속에서 일부 긍정적 전망도 있으나, 실적 발표 대기 및 주의 필요.</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>['주가조작', '실적', '하락']</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>010140</t>
         </is>
       </c>
     </row>
